--- a/xlsx/packagedata20260426 lcl some rotatable en.xlsx
+++ b/xlsx/packagedata20260426 lcl some rotatable en.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Collection\ReactThreejsFiber\Containerloadingsys\public\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F42A67-AE31-40DD-9CDF-22C8F15964DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F57446D5-A52C-406D-8E61-1A9C33832931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
